--- a/frontend/public/templates/subscribers-template.xlsx
+++ b/frontend/public/templates/subscribers-template.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaysh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaysh\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACC9AC6-1DA8-4D82-BB93-FEC3BEBE680D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B771466-C705-43EE-9368-0E77E7B411FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{EE73EB6A-C9FC-4263-8547-F8301447DD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$O$86</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Site Name</t>
   </si>
@@ -69,55 +72,46 @@
     <t>Password</t>
   </si>
   <si>
+    <t>Zudio, Signature Business Park, Near New Karond Mandi, New Bhanpur Bridge Road, opposite Kamla Devi Public School, Karond, Bhopal, Madhya Pradesh- 462018</t>
+  </si>
+  <si>
+    <t>Aspirare</t>
+  </si>
+  <si>
+    <t>Z546</t>
+  </si>
+  <si>
+    <t>Airtel_vika_0820</t>
+  </si>
+  <si>
+    <t>Air@01174</t>
+  </si>
+  <si>
+    <t>Airtel - Abdul Hafeez Khan</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>40 Mbps</t>
+  </si>
+  <si>
+    <t>Account ID</t>
+  </si>
+  <si>
+    <t>Circuit ID</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
     <t>Zudio</t>
   </si>
   <si>
-    <t>Z1</t>
-  </si>
-  <si>
-    <t>Jaisilan</t>
-  </si>
-  <si>
-    <t>Airtel AirFiber</t>
-  </si>
-  <si>
-    <t>50Mbps</t>
-  </si>
-  <si>
-    <t>Z2</t>
-  </si>
-  <si>
-    <t>Z3</t>
-  </si>
-  <si>
-    <t>Z4</t>
-  </si>
-  <si>
-    <t>Z5</t>
-  </si>
-  <si>
-    <t>Z6</t>
-  </si>
-  <si>
-    <t>100Mbps</t>
-  </si>
-  <si>
-    <t>Zudio, Signature Business Park, Near New Karond Mandi, New Bhanpur Bridge Road, opposite Kamla Devi Public School, Karond, Bhopal, Madhya Pradesh- 462018</t>
-  </si>
-  <si>
-    <t>Mamco Tower Mamco Project LLP, Thamarassery, Karadi, Kozhikode, Kerala - 673573</t>
-  </si>
-  <si>
-    <t>No-7-7-4, V.D. Road, Hindupur, Andhra Pradesh, Pin- 515201</t>
-  </si>
-  <si>
-    <t>D. No: 2, 1-60, Koppana Complese, Bhanugudi Junction, Srinagar, Kakinada, Andhra Pradesh ,Pin -533003</t>
-  </si>
-  <si>
-    <t>Datta Estates, 17-11-12, Fort Road, Vizianagaram, Andhra Pradesh, Pin-535002</t>
-  </si>
-  <si>
-    <t>Hariom Tower, Near New Bus Stand, Sekhrakhedi Road, Zone – 1, No – 4, House No – 353, Sehore, Madhya Pradesh, Pin code – 466001</t>
+    <t>0846824596017_wifi</t>
+  </si>
+  <si>
+    <t>ASR-183</t>
   </si>
 </sst>
 </file>
@@ -147,12 +141,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -182,17 +182,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF481D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -501,296 +538,965 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A212F020-0B0D-40CB-B5CA-DA0422D826E5}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.88671875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="P1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>9819712327</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="6">
+        <v>7400450767</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="6">
+        <v>8269056889</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>3002</v>
+      </c>
+      <c r="M2" s="9">
+        <v>45630</v>
+      </c>
+      <c r="N2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G2">
-        <v>8968778891</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="O2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>500</v>
-      </c>
-      <c r="K2">
-        <v>1499</v>
-      </c>
-      <c r="L2" s="2">
-        <v>45815</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="P2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <v>9819712327</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>8968778891</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>400</v>
-      </c>
-      <c r="K3">
-        <v>3000</v>
-      </c>
-      <c r="L3" s="2">
-        <v>45815</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="Q2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>9819712327</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>8968778891</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>500</v>
-      </c>
-      <c r="K4">
-        <v>499</v>
-      </c>
-      <c r="L4" s="2">
-        <v>45815</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <v>9819712327</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5">
-        <v>8968778891</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>500</v>
-      </c>
-      <c r="K5">
-        <v>600</v>
-      </c>
-      <c r="L5" s="2">
-        <v>45817</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>9819712327</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>8968778891</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>500</v>
-      </c>
-      <c r="K6">
-        <v>1499</v>
-      </c>
-      <c r="L6" s="2">
-        <v>45818</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>9819712327</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7">
-        <v>8968778891</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1500</v>
-      </c>
-      <c r="K7">
-        <v>499</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45819</v>
-      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+    </row>
+    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+    </row>
+    <row r="18" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+    </row>
+    <row r="19" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+    </row>
+    <row r="21" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+    </row>
+    <row r="23" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+    </row>
+    <row r="24" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+    </row>
+    <row r="25" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+    </row>
+    <row r="26" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+    </row>
+    <row r="27" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+    </row>
+    <row r="28" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+    </row>
+    <row r="29" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+    </row>
+    <row r="30" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+    </row>
+    <row r="31" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+      <c r="K32"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+    </row>
+    <row r="34" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+    </row>
+    <row r="35" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+    </row>
+    <row r="37" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+    </row>
+    <row r="39" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+    </row>
+    <row r="40" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+    </row>
+    <row r="41" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+    </row>
+    <row r="42" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+    </row>
+    <row r="43" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+    </row>
+    <row r="44" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+    </row>
+    <row r="45" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+    </row>
+    <row r="46" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+    </row>
+    <row r="47" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+    </row>
+    <row r="48" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+    </row>
+    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+    </row>
+    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+    </row>
+    <row r="55" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+    </row>
+    <row r="56" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+    </row>
+    <row r="57" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+    </row>
+    <row r="58" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+    </row>
+    <row r="59" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+    </row>
+    <row r="60" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+    </row>
+    <row r="61" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+    </row>
+    <row r="62" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+    </row>
+    <row r="63" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63"/>
+    </row>
+    <row r="64" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+    </row>
+    <row r="65" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+    </row>
+    <row r="66" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+    </row>
+    <row r="67" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+    </row>
+    <row r="68" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+    </row>
+    <row r="69" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+    </row>
+    <row r="70" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+    </row>
+    <row r="71" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+    </row>
+    <row r="72" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+    </row>
+    <row r="73" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+    </row>
+    <row r="74" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+    </row>
+    <row r="75" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
+    </row>
+    <row r="76" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76"/>
+    </row>
+    <row r="77" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+    </row>
+    <row r="78" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78"/>
+      <c r="L78"/>
+      <c r="M78"/>
+      <c r="N78"/>
+    </row>
+    <row r="79" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
+      <c r="N79"/>
+    </row>
+    <row r="80" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80"/>
+      <c r="L80"/>
+      <c r="M80"/>
+      <c r="N80"/>
+    </row>
+    <row r="81" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+    </row>
+    <row r="82" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82"/>
+      <c r="L82"/>
+      <c r="M82"/>
+      <c r="N82"/>
+    </row>
+    <row r="83" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+      <c r="N83"/>
+    </row>
+    <row r="84" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+      <c r="K84"/>
+      <c r="L84"/>
+      <c r="M84"/>
+      <c r="N84"/>
+    </row>
+    <row r="85" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
+      <c r="N85"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:O86" xr:uid="{6E92232E-CDA1-4836-AF80-F157E274917E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
